--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.53527</v>
+        <v>17.60067</v>
       </c>
       <c r="D2" t="n">
-        <v>17.07713</v>
+        <v>17.47305</v>
       </c>
       <c r="E2" t="n">
-        <v>17.39092</v>
+        <v>17.49541</v>
       </c>
       <c r="F2" t="n">
-        <v>44.53517</v>
+        <v>44.57746</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05301</v>
+        <v>0.0524</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91436</v>
+        <v>1.85169</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.69884</v>
+        <v>17.8072</v>
       </c>
       <c r="D3" t="n">
-        <v>17.40001</v>
+        <v>17.23079</v>
       </c>
       <c r="E3" t="n">
-        <v>17.40837</v>
+        <v>17.63764</v>
       </c>
       <c r="F3" t="n">
-        <v>44.01681</v>
+        <v>43.59548</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0527</v>
+        <v>0.05175</v>
       </c>
       <c r="H3" t="n">
-        <v>1.90741</v>
+        <v>1.94134</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.86883</v>
+        <v>17.44208</v>
       </c>
       <c r="D4" t="n">
-        <v>17.4257</v>
+        <v>17.26742</v>
       </c>
       <c r="E4" t="n">
-        <v>18.08985</v>
+        <v>17.34756</v>
       </c>
       <c r="F4" t="n">
-        <v>43.88209</v>
+        <v>45.62014</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05422</v>
+        <v>0.05323</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91351</v>
+        <v>1.87405</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.29528</v>
+        <v>17.49991</v>
       </c>
       <c r="D6" t="n">
-        <v>16.71489</v>
+        <v>16.53397</v>
       </c>
       <c r="E6" t="n">
-        <v>17.18942</v>
+        <v>17.48874</v>
       </c>
       <c r="F6" t="n">
-        <v>22.57004</v>
+        <v>22.77722</v>
       </c>
       <c r="G6" t="n">
-        <v>35.19205</v>
+        <v>34.67415</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.20903</v>
+        <v>17.8595</v>
       </c>
       <c r="D7" t="n">
-        <v>16.8781</v>
+        <v>16.88246</v>
       </c>
       <c r="E7" t="n">
-        <v>17.20409</v>
+        <v>17.45128</v>
       </c>
       <c r="F7" t="n">
-        <v>22.56136</v>
+        <v>22.94223</v>
       </c>
       <c r="G7" t="n">
-        <v>35.05119</v>
+        <v>35.50137</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.52431</v>
+        <v>17.77474</v>
       </c>
       <c r="D8" t="n">
-        <v>16.43471</v>
+        <v>16.87453</v>
       </c>
       <c r="E8" t="n">
-        <v>17.03623</v>
+        <v>17.0154</v>
       </c>
       <c r="F8" t="n">
-        <v>23.01437</v>
+        <v>22.77599</v>
       </c>
       <c r="G8" t="n">
-        <v>35.2122</v>
+        <v>36.00528</v>
       </c>
     </row>
   </sheetData>
